--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -4427,7 +4427,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -19632,38 +19632,30 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H299" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I299" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H299" s="5" t="n">
+        <v>13189000</v>
+      </c>
+      <c r="I299" s="5" t="n">
+        <v>23017</v>
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K299" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L299" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K299" s="5" t="n">
+        <v>13189000</v>
+      </c>
+      <c r="L299" s="5" t="n">
+        <v>23017</v>
       </c>
       <c r="M299" s="3" t="inlineStr">
         <is>
@@ -19672,7 +19664,7 @@
       </c>
       <c r="N299" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39397,7 +39389,7 @@
           <t>G | 538呎 (2房)
 $1111万
 $20,654/呎
-(26年-08月-09日)</t>
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -40746,7 +40738,7 @@
           <t>G | 538呎 (2房)
 $993万
 $18,454/呎
-(26年-08月-08日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -41473,7 +41465,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41483,7 +41475,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -41677,12 +41669,12 @@
 (26年-05月-14日)</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1319万
+$23,017/呎
+(26年-09月-07日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -4939,7 +4939,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20925,7 +20925,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -23765,7 +23765,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -28567,7 +28567,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -32013,7 +32013,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -39460,7 +39460,7 @@
           <t>G | 538呎 (2房)
 $1102万
 $20,491/呎
-(26年-08月-15日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -40241,7 +40241,7 @@
           <t>G | 538呎 (2房)
 $1028万
 $19,110/呎
-(26年-08月-18日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -41713,7 +41713,7 @@
           <t>D | 538呎 (2房)
 $988万
 $18,357/呎
-(26年-08月-23日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -41784,7 +41784,7 @@
           <t>D | 538呎 (2房)
 $984万
 $18,284/呎
-(26年-08月-18日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -42242,7 +42242,7 @@
           <t>H | 573呎 (2房)
 $1187万
 $20,717/呎
-(26年-08月-18日)</t>
+(26年-09月-09日)</t>
         </is>
       </c>
     </row>
@@ -42313,7 +42313,7 @@
           <t>H | 573呎 (2房)
 $1178万
 $20,555/呎
-(26年-08月-15日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -42857,7 +42857,7 @@
           <t>E | 537呎 (2房)
 $910万
 $16,953/呎
-(26年-08月-23日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -43378,7 +43378,7 @@
           <t>H | 573呎 (2房)
 $1077万
 $18,791/呎
-(26年-08月-24日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -835,7 +835,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -25425,7 +25425,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -25937,7 +25937,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -26837,7 +26837,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -28047,7 +28047,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -31488,38 +31488,30 @@
       </c>
       <c r="F483" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H483" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I483" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H483" s="5" t="n">
+        <v>10848000</v>
+      </c>
+      <c r="I483" s="5" t="n">
+        <v>18932</v>
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K483" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L483" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K483" s="5" t="n">
+        <v>10848000</v>
+      </c>
+      <c r="L483" s="5" t="n">
+        <v>18932</v>
       </c>
       <c r="M483" s="3" t="inlineStr">
         <is>
@@ -31528,7 +31520,7 @@
       </c>
       <c r="N483" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38892,7 +38884,7 @@
           <t>G | 538呎 (2房)
 $1195万
 $22,208/呎
-(26年-08月-16日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr">
@@ -39602,7 +39594,7 @@
           <t>G | 538呎 (2房)
 $1085万
 $20,165/呎
-(26年-08月-18日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -40099,7 +40091,7 @@
           <t>G | 538呎 (2房)
 $1038万
 $19,301/呎
-(26年-08月-16日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -41465,7 +41457,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41475,7 +41467,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>191</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -42439,7 +42431,7 @@
           <t>F | 512呎 (2房)
 $887万
 $17,328/呎
-(26年-08月-24日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -42510,7 +42502,7 @@
           <t>F | 512呎 (2房)
 $884万
 $17,260/呎
-(26年-08月-23日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -42668,7 +42660,7 @@
           <t>H | 573呎 (2房)
 $1137万
 $19,843/呎
-(26年-08月-22日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -42786,7 +42778,7 @@
           <t>E | 537呎 (2房)
 $914万
 $17,019/呎
-(26年-08月-24日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -43302,12 +43294,12 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1085万
+$18,932/呎
+(26年-09月-13日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -6987,7 +6987,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -24789,7 +24789,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24913,7 +24913,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -25813,7 +25813,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -30127,7 +30127,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -39736,7 +39736,7 @@
           <t>G | 538呎 (2房)
 $1068万
 $19,848/呎
-(26年-08月-20日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -39878,7 +39878,7 @@
           <t>G | 538呎 (2房)
 $1054万
 $19,591/呎
-(26年-08月-25日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -40162,7 +40162,7 @@
           <t>G | 538呎 (2房)
 $1033万
 $19,204/呎
-(26年-08月-16日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -41563,7 +41563,7 @@
           <t>D | 538呎 (2房)
 $1002万
 $18,615/呎
-(26年-08月-23日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -42360,7 +42360,7 @@
           <t>F | 512呎 (2房)
 $891万
 $17,398/呎
-(26年-08月-25日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -42376,7 +42376,7 @@
           <t>H | 573呎 (2房)
 $1168万
 $20,391/呎
-(26年-08月-26日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -42518,7 +42518,7 @@
           <t>H | 573呎 (2房)
 $1150万
 $20,068/呎
-(26年-08月-27日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
     </row>
@@ -43062,7 +43062,7 @@
           <t>E | 537呎 (2房)
 $900万
 $16,750/呎
-(26年-08月-15日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -33541,7 +33541,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H515" s="5" t="n">
@@ -39523,7 +39523,7 @@
           <t>G | 538呎 (2房)
 $1094万
 $20,327/呎
-(26年-08月-17日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -39949,7 +39949,7 @@
           <t>G | 538呎 (2房)
 $1049万
 $19,494/呎
-(26年-08月-25日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -43583,7 +43583,7 @@
           <t>H | 573呎 (2房)
 $1061万
 $18,511/呎
-(26年-08月-22日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -9043,7 +9043,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -27861,7 +27861,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -40020,7 +40020,7 @@
           <t>G | 538呎 (2房)
 $1044万
 $19,396/呎
-(26年-08月-25日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -42707,7 +42707,7 @@
           <t>E | 537呎 (2房)
 $918万
 $17,088/呎
-(26年-08月-30日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -42802,7 +42802,7 @@
           <t>H | 573呎 (2房)
 $1120万
 $19,555/呎
-(26年-08月-30日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -19637,7 +19637,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -26506,34 +26506,34 @@
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
-        <v>10882000</v>
+        <v>9250000</v>
       </c>
       <c r="I406" s="5" t="n">
-        <v>20264</v>
+        <v>17225</v>
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K406" s="5" t="n">
-        <v>9249700</v>
+        <v>9250000</v>
       </c>
       <c r="L406" s="5" t="n">
         <v>17225</v>
       </c>
       <c r="M406" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N406" s="3" t="inlineStr">
@@ -41457,7 +41457,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41467,7 +41467,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>192</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -41666,7 +41666,7 @@
           <t>H | 573呎 (2房)
 $1319万
 $23,017/呎
-(26年-09月-07日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -42560,12 +42560,12 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1088万
-$20,264/呎
-(在售)</t>
+$925万
+$17,225/呎
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -20664,38 +20664,30 @@
       </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H315" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I315" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H315" s="5" t="n">
+        <v>12689000</v>
+      </c>
+      <c r="I315" s="5" t="n">
+        <v>22145</v>
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K315" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L315" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K315" s="5" t="n">
+        <v>12689000</v>
+      </c>
+      <c r="L315" s="5" t="n">
+        <v>22145</v>
       </c>
       <c r="M315" s="3" t="inlineStr">
         <is>
@@ -20704,7 +20696,7 @@
       </c>
       <c r="N315" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21184,38 +21176,30 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H323" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I323" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="H323" s="5" t="n">
+        <v>12464000</v>
+      </c>
+      <c r="I323" s="5" t="n">
+        <v>21752</v>
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K323" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L323" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K323" s="5" t="n">
+        <v>12464000</v>
+      </c>
+      <c r="L323" s="5" t="n">
+        <v>21752</v>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
@@ -21224,7 +21208,7 @@
       </c>
       <c r="N323" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -41457,7 +41441,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41467,7 +41451,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>194</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -41803,12 +41787,12 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1269万
+$22,145/呎
+(26年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -41874,12 +41858,12 @@
 (26年-06月-02日)</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1246万
+$21,752/呎
+(26年-10月-04日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -31477,7 +31477,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -43283,7 +43283,7 @@
           <t>H | 573呎 (2房)
 $1085万
 $18,932/呎
-(26年-09月-13日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -28872,38 +28872,30 @@
       </c>
       <c r="F443" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H443" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I443" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H443" s="5" t="n">
+        <v>11094000</v>
+      </c>
+      <c r="I443" s="5" t="n">
+        <v>19361</v>
       </c>
       <c r="J443" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K443" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L443" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K443" s="5" t="n">
+        <v>11094000</v>
+      </c>
+      <c r="L443" s="5" t="n">
+        <v>19361</v>
       </c>
       <c r="M443" s="3" t="inlineStr">
         <is>
@@ -28912,7 +28904,7 @@
       </c>
       <c r="N443" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -41441,7 +41433,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41451,7 +41443,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -42923,12 +42915,12 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1109万
+$19,361/呎
+(26年-10月-13日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -20144,38 +20144,30 @@
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H307" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I307" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H307" s="5" t="n">
+        <v>12917000</v>
+      </c>
+      <c r="I307" s="5" t="n">
+        <v>22543</v>
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K307" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L307" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K307" s="5" t="n">
+        <v>12917000</v>
+      </c>
+      <c r="L307" s="5" t="n">
+        <v>22543</v>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
@@ -20184,7 +20176,7 @@
       </c>
       <c r="N307" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -20669,7 +20661,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -21181,7 +21173,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -25978,34 +25970,34 @@
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
-        <v>10926000</v>
+        <v>9287000</v>
       </c>
       <c r="I398" s="5" t="n">
-        <v>20346</v>
+        <v>17294</v>
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K398" s="5" t="n">
-        <v>9287100</v>
+        <v>9287000</v>
       </c>
       <c r="L398" s="5" t="n">
         <v>17294</v>
       </c>
       <c r="M398" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N398" s="3" t="inlineStr">
@@ -26495,7 +26487,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -28352,38 +28344,30 @@
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H435" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I435" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H435" s="5" t="n">
+        <v>11149000</v>
+      </c>
+      <c r="I435" s="5" t="n">
+        <v>19457</v>
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K435" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L435" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K435" s="5" t="n">
+        <v>11149000</v>
+      </c>
+      <c r="L435" s="5" t="n">
+        <v>19457</v>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
@@ -28392,7 +28376,7 @@
       </c>
       <c r="N435" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33005,7 +32989,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
@@ -41433,7 +41417,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41443,7 +41427,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>198</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -41708,7 +41692,1285 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1292万
+$22,543/呎
+(26年-10月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$996万
+$18,212/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$984万
+$18,284/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1137万
+$21,173/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1082万
+$21,133/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1127万
+$20,348/呎
+(26年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1269万
+$22,145/呎
+(26年-10月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$984万
+$17,996/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$980万
+$18,212/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1132万
+$21,089/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1078万
+$21,047/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1114万
+$20,106/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1246万
+$21,752/呎
+(26年-10月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$977万
+$17,854/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$976万
+$18,139/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1128万
+$21,006/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1073万
+$20,963/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1103万
+$19,908/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$973万
+$17,782/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$955万
+$17,747/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$957万
+$17,819/呎
+(26年-09月-03日)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$893万
+$17,436/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1097万
+$19,809/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1221万
+$21,304/呎
+(26年-09月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$967万
+$17,676/呎
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$949万
+$17,641/呎
+(26年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1119万
+$20,838/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$887万
+$17,330/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1084万
+$19,574/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1206万
+$21,051/呎
+(26年-08月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$963万
+$17,607/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$945万
+$17,572/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1115万
+$20,756/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$884万
+$17,262/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1076万
+$19,419/呎
+(25年-11月-27日)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1197万
+$20,883/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$959万
+$17,536/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$942万
+$17,500/呎
+(26年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1110万
+$20,672/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$880万
+$17,193/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1067万
+$19,265/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1187万
+$20,717/呎
+(26年-09月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$955万
+$17,466/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$938万
+$17,431/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1106万
+$20,590/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$877万
+$17,125/呎
+(26年-06月-09日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1059万
+$19,112/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1178万
+$20,555/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$952万
+$17,397/呎
+(25年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$934万
+$17,362/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1101万
+$20,508/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$891万
+$17,398/呎
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1050万
+$18,958/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1168万
+$20,391/呎
+(26年-09月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$937万
+$17,122/呎
+(26年-04月-14日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$930万
+$17,294/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1097万
+$20,426/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$887万
+$17,328/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1042万
+$18,809/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1159万
+$20,229/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$944万
+$17,258/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$927万
+$17,225/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$929万
+$17,294/呎
+(26年-10月-18日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$884万
+$17,260/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1034万
+$18,661/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1150万
+$20,068/呎
+(26年-09月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$940万
+$17,190/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$923万
+$17,154/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$925万
+$17,225/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$880万
+$17,191/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1026万
+$18,511/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1141万
+$19,909/呎
+(26年-08月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$938万
+$17,155/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$921万
+$17,121/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$923万
+$17,190/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$878万
+$17,156/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1022万
+$18,451/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1137万
+$19,843/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$933万
+$17,053/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$905万
+$16,818/呎
+(26年-03月-09日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$918万
+$17,088/呎
+(26年-09月-23日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$856万
+$16,719/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1012万
+$18,274/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1126万
+$19,653/呎
+(26年-08月-07日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$902万
+$16,484/呎
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$912万
+$16,952/呎
+(26年-03月-13日)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$914万
+$17,019/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$853万
+$16,652/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$996万
+$17,969/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1120万
+$19,555/呎
+(26年-09月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$914万
+$16,718/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$908万
+$16,885/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$910万
+$16,953/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$849万
+$16,586/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1002万
+$18,092/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1115万
+$19,457/呎
+(26年-10月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$922万
+$16,850/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$894万
+$16,619/呎
+(26年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$907万
+$16,885/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$846万
+$16,520/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$986万
+$17,791/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1109万
+$19,361/呎
+(26年-10月-13日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$918万
+$16,782/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$901万
+$16,751/呎
+(26年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$903万
+$16,816/呎
+(26年-09月-02日)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$842万
+$16,453/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$992万
+$17,913/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -41717,13 +42979,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41731,7 +42993,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -41739,62 +43001,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$996万
-$18,212/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
+$914万
+$16,715/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$984万
-$18,284/呎
-(26年-09月-10日)</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
+$887万
+$16,487/呎
+(26年-03月-02日)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1137万
-$21,173/呎
+$900万
+$16,750/呎
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$839万
+$16,389/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$987万
+$17,823/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1082万
-$21,133/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1127万
-$20,348/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1269万
-$22,145/呎
-(26年-10月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41802,7 +43064,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -41810,62 +43072,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$984万
-$17,996/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
+$911万
+$16,649/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$980万
-$18,212/呎
-(26年-09月-01日)</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
+$894万
+$16,615/呎
+(26年-03月-25日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1132万
-$21,089/呎
+$878万
+$16,356/呎
+(26年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$836万
+$16,324/呎
+(26年-03月-25日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$982万
+$17,735/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
 (在售)</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1078万
-$21,047/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1114万
-$20,106/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1246万
-$21,752/呎
-(26年-10月-04日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41873,7 +43135,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -41881,62 +43143,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$977万
-$17,854/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+$907万
+$16,581/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$976万
-$18,139/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
+$922万
+$17,134/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1128万
-$21,006/呎
+$875万
+$16,291/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$832万
+$16,258/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$978万
+$17,648/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1073万
-$20,963/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1103万
-$19,908/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41944,7 +43206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -41952,62 +43214,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$973万
-$17,782/呎
+$905万
+$16,550/呎
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$955万
-$17,747/呎
+$889万
+$16,517/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$873万
+$16,259/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$831万
+$16,227/呎
 (25年-10月-06日)</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$957万
-$17,819/呎
-(26年-09月-03日)</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$893万
-$17,436/呎
-(26年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1097万
-$19,809/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="I11" s="21" t="inlineStr">
+$964万
+$17,395/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1221万
-$21,304/呎
-(26年-09月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+$1085万
+$18,932/呎
+(26年-10月-06日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42015,7 +43277,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42023,62 +43285,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$967万
-$17,676/呎
-(26年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+$900万
+$16,452/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$949万
-$17,641/呎
-(26年-05月-15日)</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
+$883万
+$16,418/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1119万
-$20,838/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="inlineStr">
+$868万
+$16,162/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$887万
-$17,330/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
+$826万
+$16,131/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1084万
-$19,574/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="I12" s="21" t="inlineStr">
+$968万
+$17,471/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1206万
-$21,051/呎
-(26年-08月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
+$1077万
+$18,791/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42086,7 +43348,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42094,62 +43356,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
+$896万
+$16,384/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$870万
+$16,162/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$864万
+$16,099/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$822万
+$16,064/呎
+(26年-03月-09日)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
 $963万
-$17,607/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$945万
-$17,572/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1115万
-$20,756/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$884万
-$17,262/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1076万
-$19,419/呎
-(25年-11月-27日)</t>
-        </is>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
+$17,384/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1197万
-$20,883/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
+$1071万
+$18,696/呎
+(26年-08月-31日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42157,7 +43419,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42165,1284 +43427,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$959万
-$17,536/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$942万
-$17,500/呎
-(26年-05月-15日)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1110万
-$20,672/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G14" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$880万
-$17,193/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1067万
-$19,265/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1187万
-$20,717/呎
-(26年-09月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$955万
-$17,466/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$938万
-$17,431/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1106万
-$20,590/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G15" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$877万
-$17,125/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1059万
-$19,112/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1178万
-$20,555/呎
-(26年-09月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$952万
-$17,397/呎
-(25年-11月-21日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$934万
-$17,362/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1101万
-$20,508/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$891万
-$17,398/呎
-(26年-09月-15日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1050万
-$18,958/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1168万
-$20,391/呎
-(26年-09月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$937万
-$17,122/呎
-(26年-04月-14日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$930万
-$17,294/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1097万
-$20,426/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$887万
-$17,328/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1042万
-$18,809/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1159万
-$20,229/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$944万
-$17,258/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$927万
-$17,225/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1093万
-$20,346/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$884万
-$17,260/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1034万
-$18,661/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1150万
-$20,068/呎
-(26年-09月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$940万
-$17,190/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$923万
-$17,154/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$925万
-$17,225/呎
-(26年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$880万
-$17,191/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1026万
-$18,511/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1141万
-$19,909/呎
-(26年-08月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$938万
-$17,155/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$921万
-$17,121/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$923万
-$17,190/呎
-(26年-09月-01日)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$878万
-$17,156/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1022万
-$18,451/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1137万
-$19,843/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$933万
-$17,053/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$905万
-$16,818/呎
-(26年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$918万
-$17,088/呎
-(26年-09月-23日)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$856万
-$16,719/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1012万
-$18,274/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1126万
-$19,653/呎
-(26年-08月-07日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$902万
-$16,484/呎
-(26年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$912万
-$16,952/呎
-(26年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$914万
-$17,019/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$853万
-$16,652/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$996万
-$17,969/呎
-(26年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1120万
-$19,555/呎
-(26年-09月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$914万
-$16,718/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$908万
-$16,885/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$910万
-$16,953/呎
-(26年-09月-10日)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$849万
-$16,586/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1002万
-$18,092/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$922万
-$16,850/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$894万
-$16,619/呎
-(26年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$907万
-$16,885/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$846万
-$16,520/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$986万
-$17,791/呎
-(26年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1109万
-$19,361/呎
-(26年-10月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$918万
-$16,782/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$901万
-$16,751/呎
-(26年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$903万
-$16,816/呎
-(26年-09月-02日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$842万
-$16,453/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$992万
-$17,913/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$914万
-$16,715/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$887万
-$16,487/呎
-(26年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$900万
-$16,750/呎
-(26年-09月-15日)</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$839万
-$16,389/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$987万
-$17,823/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="I26" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$911万
-$16,649/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$894万
-$16,615/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$878万
-$16,356/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$836万
-$16,324/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$982万
-$17,735/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I27" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$907万
-$16,581/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$922万
-$17,134/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$875万
-$16,291/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$832万
-$16,258/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$978万
-$17,648/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$905万
-$16,550/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$889万
-$16,517/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$873万
-$16,259/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="G29" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$831万
-$16,227/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$964万
-$17,395/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1085万
-$18,932/呎
-(26年-10月-06日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$900万
-$16,452/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$883万
-$16,418/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$868万
-$16,162/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$826万
-$16,131/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$968万
-$17,471/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I30" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1077万
-$18,791/呎
-(26年-09月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$896万
-$16,384/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$870万
-$16,162/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$864万
-$16,099/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$822万
-$16,064/呎
-(26年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$963万
-$17,384/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1071万
-$18,696/呎
-(26年-08月-31日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
@@ -43488,7 +43472,7 @@
           <t>H | 573呎 (2房)
 $1066万
 $18,604/呎
-(26年-07月-13日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
     </row>
